--- a/artfynd/A 28406-2025 artfynd.xlsx
+++ b/artfynd/A 28406-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123325488</v>
+        <v>123325483</v>
       </c>
       <c r="B2" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600992</v>
+        <v>600945</v>
       </c>
       <c r="R2" t="n">
-        <v>6976179</v>
+        <v>6975960</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1476</t>
+          <t>2024_1481</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Sälg</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,42 +800,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123325487</v>
+        <v>123325484</v>
       </c>
       <c r="B3" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600951</v>
+        <v>600980</v>
       </c>
       <c r="R3" t="n">
-        <v>6976162</v>
+        <v>6976000</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +874,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1477</t>
+          <t>2024_1480</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flera sälgar</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -945,37 +925,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123325489</v>
+        <v>123325493</v>
       </c>
       <c r="B4" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -994,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600988</v>
+        <v>600891</v>
       </c>
       <c r="R4" t="n">
-        <v>6976234</v>
+        <v>6976254</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +999,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1475</t>
+          <t>2024_1471</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1019,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Vid ledningsgatan</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1080,47 +1055,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123325491</v>
+        <v>123325486</v>
       </c>
       <c r="B5" t="n">
-        <v>97996</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1129,10 +1099,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600902</v>
+        <v>600887</v>
       </c>
       <c r="R5" t="n">
-        <v>6976262</v>
+        <v>6976126</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1129,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1473</t>
+          <t>2024_1478</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1139,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,12 +1149,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1204,7 +1169,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1215,15 +1180,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123325483</v>
+        <v>123325487</v>
       </c>
       <c r="B6" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,31 +1191,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1264,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600945</v>
+        <v>600951</v>
       </c>
       <c r="R6" t="n">
-        <v>6975960</v>
+        <v>6976162</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1294,7 +1254,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1481</t>
+          <t>2024_1477</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1304,7 +1264,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1314,7 +1274,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera sälgar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1334,7 +1299,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1345,15 +1310,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123325492</v>
+        <v>123325488</v>
       </c>
       <c r="B7" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1340,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1394,10 +1354,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600922</v>
+        <v>600992</v>
       </c>
       <c r="R7" t="n">
-        <v>6976277</v>
+        <v>6976179</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1424,7 +1384,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1472</t>
+          <t>2024_1476</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1434,7 +1394,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1444,12 +1404,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>på sälg</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1480,15 +1440,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123325484</v>
+        <v>123325489</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1496,26 +1451,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1529,10 +1484,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600980</v>
+        <v>600988</v>
       </c>
       <c r="R8" t="n">
-        <v>6976000</v>
+        <v>6976234</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1559,7 +1514,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1480</t>
+          <t>2024_1475</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1569,7 +1524,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1579,7 +1534,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1599,7 +1559,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1610,37 +1570,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123325485</v>
+        <v>123325492</v>
       </c>
       <c r="B9" t="n">
-        <v>58351</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208249</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1650,7 +1605,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1659,10 +1614,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600882</v>
+        <v>600922</v>
       </c>
       <c r="R9" t="n">
-        <v>6976117</v>
+        <v>6976277</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1689,7 +1644,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1479</t>
+          <t>2024_1472</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1699,7 +1654,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1709,12 +1664,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
+          <t>på sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1745,47 +1700,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123325493</v>
+        <v>123325485</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1794,10 +1744,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600891</v>
+        <v>600882</v>
       </c>
       <c r="R10" t="n">
-        <v>6976254</v>
+        <v>6976117</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1824,7 +1774,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1471</t>
+          <t>2024_1479</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1834,7 +1784,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1844,12 +1794,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Vid ledningsgatan</t>
+          <t>Sumpskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1883,12 +1833,7 @@
         <v>123325490</v>
       </c>
       <c r="B11" t="n">
-        <v>58351</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2015,47 +1960,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123325486</v>
+        <v>123325491</v>
       </c>
       <c r="B12" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2064,10 +2004,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600887</v>
+        <v>600902</v>
       </c>
       <c r="R12" t="n">
-        <v>6976126</v>
+        <v>6976262</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2094,7 +2034,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1478</t>
+          <t>2024_1473</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2104,7 +2044,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2114,7 +2054,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2134,7 +2079,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">

--- a/artfynd/A 28406-2025 artfynd.xlsx
+++ b/artfynd/A 28406-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325483</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325484</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1052,6 +1067,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325493</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1177,6 +1197,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325486</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1307,6 +1332,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325487</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1437,6 +1467,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325488</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1567,6 +1602,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325489</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1697,6 +1737,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325492</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1827,6 +1872,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325485</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1957,6 +2007,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325490</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2087,8 +2142,26 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325491</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>